--- a/public/informes-templates/INFORME DE DE PLC.xlsx
+++ b/public/informes-templates/INFORME DE DE PLC.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2C95DA-2E50-4D9A-A700-6C6EFF3883AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3A6598-C61A-4520-BED6-54459DE588CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>INFORME DE SERVICIO</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>FECHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EQUIPO 1 </t>
   </si>
   <si>
     <t>DATOS DEL EQUIPO</t>
@@ -456,90 +453,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -566,6 +479,90 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -841,17 +838,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="18"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -871,15 +868,15 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="12"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="36"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -899,17 +896,17 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="9"/>
+      <c r="A3" s="41"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="18"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -929,17 +926,17 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="9"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -959,17 +956,17 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="9"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -989,17 +986,17 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1019,17 +1016,17 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1049,17 +1046,17 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1079,17 +1076,17 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1109,17 +1106,17 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="9"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1139,17 +1136,17 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="9"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1169,15 +1166,15 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1197,12 +1194,10 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="32"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="26" t="s">
         <v>10</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="20" t="s">
-        <v>11</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
@@ -1229,26 +1224,26 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="34"/>
       <c r="C14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="26" t="s">
         <v>13</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>14</v>
       </c>
       <c r="F14" s="22"/>
       <c r="G14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1269,11 +1264,11 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="23"/>
+      <c r="E15" s="24"/>
       <c r="F15" s="22"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -1297,19 +1292,19 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="24"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="9"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="18"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1329,15 +1324,15 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="12"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="36"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1357,8 +1352,8 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
-        <v>20</v>
+      <c r="A18" s="29" t="s">
+        <v>19</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
@@ -1387,15 +1382,15 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="37"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="9"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1415,15 +1410,15 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="12"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1443,15 +1438,15 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="38"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1471,15 +1466,15 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="38"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1499,15 +1494,15 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="38"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1527,15 +1522,15 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="38"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1555,15 +1550,15 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="38"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1583,15 +1578,15 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="38"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="12"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1611,15 +1606,15 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1639,15 +1634,15 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="12"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1667,15 +1662,15 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="38"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="12"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1695,15 +1690,15 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="38"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="12"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1723,15 +1718,15 @@
       <c r="Z30" s="1"/>
     </row>
     <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="38"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="40"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="12"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1751,15 +1746,15 @@
       <c r="Z31" s="1"/>
     </row>
     <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="38"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="40"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="12"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -1779,15 +1774,15 @@
       <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="38"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="40"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="12"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1807,15 +1802,15 @@
       <c r="Z33" s="1"/>
     </row>
     <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="38"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="40"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="12"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -1835,15 +1830,15 @@
       <c r="Z34" s="1"/>
     </row>
     <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="38"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="40"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="12"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1863,15 +1858,15 @@
       <c r="Z35" s="1"/>
     </row>
     <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="38"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="40"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="12"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -1891,15 +1886,15 @@
       <c r="Z36" s="1"/>
     </row>
     <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="38"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="40"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="12"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -1919,15 +1914,15 @@
       <c r="Z37" s="1"/>
     </row>
     <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="38"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="43"/>
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="15"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -1948,17 +1943,17 @@
     </row>
     <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="22"/>
       <c r="D39" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="22"/>
       <c r="G39" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H39" s="21"/>
       <c r="I39" s="22"/>
@@ -1981,15 +1976,15 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="35"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="37"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="9"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2009,15 +2004,15 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="38"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="40"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="12"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2037,15 +2032,15 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="38"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="40"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="40"/>
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="12"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -2065,15 +2060,15 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="38"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="40"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="12"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -2093,15 +2088,15 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="38"/>
-      <c r="B44" s="39"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="40"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="12"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -2121,15 +2116,15 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="38"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="40"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="12"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -2149,15 +2144,15 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="38"/>
-      <c r="B46" s="39"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="40"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="12"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -2177,15 +2172,15 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="38"/>
-      <c r="B47" s="39"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="39"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="40"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="12"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -2205,15 +2200,15 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="38"/>
-      <c r="B48" s="39"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="40"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="12"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -2233,15 +2228,15 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="38"/>
-      <c r="B49" s="39"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="40"/>
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="12"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -2261,15 +2256,15 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="38"/>
-      <c r="B50" s="39"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="39"/>
-      <c r="I50" s="40"/>
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="12"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -2289,15 +2284,15 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="38"/>
-      <c r="B51" s="39"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="40"/>
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="12"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -2317,15 +2312,15 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="38"/>
-      <c r="B52" s="39"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="40"/>
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="12"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -2345,15 +2340,15 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="38"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="40"/>
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="12"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -2373,15 +2368,15 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="38"/>
-      <c r="B54" s="39"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="40"/>
+      <c r="A54" s="10"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="12"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -2401,15 +2396,15 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="38"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="40"/>
+      <c r="A55" s="10"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="12"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -2429,15 +2424,15 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="38"/>
-      <c r="B56" s="39"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="40"/>
+      <c r="A56" s="10"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="12"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -2457,15 +2452,15 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="38"/>
-      <c r="B57" s="39"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="39"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="39"/>
-      <c r="I57" s="40"/>
+      <c r="A57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="12"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -2485,15 +2480,15 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="38"/>
-      <c r="B58" s="39"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="39"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="40"/>
+      <c r="A58" s="10"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="12"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -2513,15 +2508,15 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="38"/>
-      <c r="B59" s="39"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="43"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="42"/>
-      <c r="I59" s="43"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="15"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -2542,17 +2537,17 @@
     </row>
     <row r="60" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="22"/>
       <c r="D60" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="22"/>
       <c r="G60" s="28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H60" s="21"/>
       <c r="I60" s="22"/>
@@ -2603,8 +2598,8 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="29" t="s">
-        <v>27</v>
+      <c r="A62" s="27" t="s">
+        <v>26</v>
       </c>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
@@ -2636,8 +2631,8 @@
       <c r="A63" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B63" s="20" t="s">
-        <v>28</v>
+      <c r="B63" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
@@ -2666,7 +2661,7 @@
     </row>
     <row r="64" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
-      <c r="B64" s="23"/>
+      <c r="B64" s="24"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
@@ -2694,7 +2689,7 @@
     </row>
     <row r="65" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
-      <c r="B65" s="23"/>
+      <c r="B65" s="24"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
@@ -2722,7 +2717,7 @@
     </row>
     <row r="66" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
-      <c r="B66" s="23"/>
+      <c r="B66" s="24"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
@@ -2750,7 +2745,7 @@
     </row>
     <row r="67" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
-      <c r="B67" s="23"/>
+      <c r="B67" s="24"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
@@ -2777,17 +2772,17 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="30" t="s">
-        <v>29</v>
+      <c r="A68" s="25" t="s">
+        <v>28</v>
       </c>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="9"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="18"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -2808,10 +2803,10 @@
     </row>
     <row r="69" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B69" s="26" t="s">
         <v>30</v>
-      </c>
-      <c r="B69" s="20" t="s">
-        <v>31</v>
       </c>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
@@ -2819,10 +2814,10 @@
       <c r="F69" s="21"/>
       <c r="G69" s="21"/>
       <c r="H69" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -2846,8 +2841,8 @@
       <c r="A70" s="6">
         <v>1</v>
       </c>
-      <c r="B70" s="31" t="s">
-        <v>34</v>
+      <c r="B70" s="23" t="s">
+        <v>33</v>
       </c>
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
@@ -2878,8 +2873,8 @@
       <c r="A71" s="6">
         <v>2</v>
       </c>
-      <c r="B71" s="31" t="s">
-        <v>35</v>
+      <c r="B71" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
@@ -2910,8 +2905,8 @@
       <c r="A72" s="6">
         <v>3</v>
       </c>
-      <c r="B72" s="31" t="s">
-        <v>36</v>
+      <c r="B72" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="C72" s="21"/>
       <c r="D72" s="21"/>
@@ -2942,8 +2937,8 @@
       <c r="A73" s="6">
         <v>4</v>
       </c>
-      <c r="B73" s="31" t="s">
-        <v>37</v>
+      <c r="B73" s="23" t="s">
+        <v>36</v>
       </c>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
@@ -2974,8 +2969,8 @@
       <c r="A74" s="6">
         <v>5</v>
       </c>
-      <c r="B74" s="31" t="s">
-        <v>38</v>
+      <c r="B74" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
@@ -3006,8 +3001,8 @@
       <c r="A75" s="6">
         <v>6</v>
       </c>
-      <c r="B75" s="31" t="s">
-        <v>39</v>
+      <c r="B75" s="23" t="s">
+        <v>38</v>
       </c>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
@@ -3038,8 +3033,8 @@
       <c r="A76" s="6">
         <v>7</v>
       </c>
-      <c r="B76" s="31" t="s">
-        <v>40</v>
+      <c r="B76" s="23" t="s">
+        <v>39</v>
       </c>
       <c r="C76" s="21"/>
       <c r="D76" s="21"/>
@@ -3070,8 +3065,8 @@
       <c r="A77" s="6">
         <v>8</v>
       </c>
-      <c r="B77" s="31" t="s">
-        <v>41</v>
+      <c r="B77" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="C77" s="21"/>
       <c r="D77" s="21"/>
@@ -3099,17 +3094,17 @@
       <c r="Z77" s="1"/>
     </row>
     <row r="78" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="32" t="s">
-        <v>42</v>
+      <c r="A78" s="19" t="s">
+        <v>41</v>
       </c>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="9"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="17"/>
+      <c r="H78" s="17"/>
+      <c r="I78" s="18"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
@@ -3129,15 +3124,15 @@
       <c r="Z78" s="1"/>
     </row>
     <row r="79" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="33"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="9"/>
+      <c r="A79" s="16"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17"/>
+      <c r="H79" s="17"/>
+      <c r="I79" s="18"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -3157,17 +3152,17 @@
       <c r="Z79" s="1"/>
     </row>
     <row r="80" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="32" t="s">
-        <v>43</v>
+      <c r="A80" s="19" t="s">
+        <v>42</v>
       </c>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="9"/>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="17"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="18"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -3187,15 +3182,15 @@
       <c r="Z80" s="1"/>
     </row>
     <row r="81" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="33"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="9"/>
+      <c r="A81" s="16"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="18"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -3215,15 +3210,15 @@
       <c r="Z81" s="1"/>
     </row>
     <row r="82" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="33"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="9"/>
+      <c r="A82" s="16"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="17"/>
+      <c r="G82" s="17"/>
+      <c r="H82" s="17"/>
+      <c r="I82" s="18"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -3243,17 +3238,17 @@
       <c r="Z82" s="1"/>
     </row>
     <row r="83" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="32" t="s">
-        <v>44</v>
+      <c r="A83" s="19" t="s">
+        <v>43</v>
       </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="9"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="17"/>
+      <c r="H83" s="17"/>
+      <c r="I83" s="18"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
@@ -3273,7 +3268,7 @@
       <c r="Z83" s="1"/>
     </row>
     <row r="84" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="34"/>
+      <c r="A84" s="20"/>
       <c r="B84" s="21"/>
       <c r="C84" s="21"/>
       <c r="D84" s="21"/>
@@ -3301,7 +3296,7 @@
       <c r="Z84" s="1"/>
     </row>
     <row r="85" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="34"/>
+      <c r="A85" s="20"/>
       <c r="B85" s="21"/>
       <c r="C85" s="21"/>
       <c r="D85" s="21"/>
@@ -7558,44 +7553,6 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A84:I84"/>
-    <mergeCell ref="A85:I85"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="A78:I78"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A81:I81"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B67:I67"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B64:I64"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="G60:I60"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A13:B17"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:I17"/>
-    <mergeCell ref="D16:D17"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A3:B11"/>
     <mergeCell ref="D3:I3"/>
@@ -7607,6 +7564,44 @@
     <mergeCell ref="D9:I9"/>
     <mergeCell ref="D10:I10"/>
     <mergeCell ref="D11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A13:B17"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:I17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="G60:I60"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="B67:I67"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="B77:G77"/>
+    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A81:I81"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/public/informes-templates/INFORME DE DE PLC.xlsx
+++ b/public/informes-templates/INFORME DE DE PLC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3A6598-C61A-4520-BED6-54459DE588CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EE1FFF-0E4B-462D-A41D-3BE5464B6BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,36 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
-  <si>
-    <t>INFORME DE SERVICIO</t>
-  </si>
-  <si>
-    <t>EMPRESA / CLIENTE</t>
-  </si>
-  <si>
-    <t>CONTACTO</t>
-  </si>
-  <si>
-    <t>ORDEN DE COMPRA</t>
-  </si>
-  <si>
-    <t>COT</t>
-  </si>
-  <si>
-    <t>LINEA / AREA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">DESCRIPCION </t>
   </si>
   <si>
-    <t>TIPO</t>
-  </si>
-  <si>
     <t>CANTIDAD</t>
-  </si>
-  <si>
-    <t>FECHA</t>
   </si>
   <si>
     <t>DATOS DEL EQUIPO</t>
@@ -153,7 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,28 +162,8 @@
     <font>
       <b/>
       <i/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -236,8 +192,16 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,6 +224,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -433,15 +403,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -453,34 +420,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -489,11 +429,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -501,68 +459,116 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -579,55 +585,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -831,24 +788,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z236"/>
+  <dimension ref="A1:Z238"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="18"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="11"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -868,15 +825,15 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="36"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="14"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -896,17 +853,15 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -926,17 +881,15 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="42"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -956,17 +909,17 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+      <c r="A5" s="41" t="s">
+        <v>2</v>
       </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
       <c r="D5" s="42"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="43"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -986,17 +939,27 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1018,15 +981,13 @@
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1046,17 +1007,19 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
+      <c r="A8" s="2" t="s">
+        <v>9</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
+      <c r="B8" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="37"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1076,17 +1039,15 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="40"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1106,12 +1067,12 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
+      <c r="A10" s="23" t="s">
+        <v>11</v>
       </c>
-      <c r="D10" s="42"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
@@ -1136,17 +1097,15 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="18"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="46"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1166,15 +1125,15 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
+      <c r="A12" s="47"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="49"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1194,17 +1153,15 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="22"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="49"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1224,27 +1181,15 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="49"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1264,15 +1209,15 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="A15" s="47"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="49"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1292,19 +1237,15 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="37"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="18"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="49"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1324,15 +1265,15 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="36"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="49"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1352,17 +1293,15 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="22"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="49"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1382,15 +1321,15 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="49"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1410,15 +1349,15 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="49"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1438,15 +1377,15 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="49"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1466,15 +1405,15 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="49"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1494,15 +1433,15 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="49"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1522,15 +1461,15 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="49"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1550,15 +1489,15 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="49"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1578,15 +1517,15 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="49"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1606,15 +1545,15 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="49"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1634,15 +1573,15 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="12"/>
+      <c r="A28" s="47"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="49"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1662,15 +1601,15 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
+      <c r="A29" s="47"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="49"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1690,15 +1629,15 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="12"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="52"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1717,16 +1656,22 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="18"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1745,16 +1690,16 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="44"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="46"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -1773,16 +1718,16 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
+    <row r="33" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="47"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="49"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1801,16 +1746,16 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
+    <row r="34" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="47"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="49"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -1829,16 +1774,16 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
+    <row r="35" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="47"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="49"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1857,16 +1802,16 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="12"/>
+    <row r="36" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="47"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="49"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -1885,16 +1830,16 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
+    <row r="37" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="47"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="49"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -1913,16 +1858,16 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15"/>
+    <row r="38" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="47"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="49"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -1942,21 +1887,15 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="21"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" s="21"/>
-      <c r="I39" s="22"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="49"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -1976,15 +1915,15 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="9"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="49"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2004,15 +1943,15 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="12"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="49"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2032,15 +1971,15 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="12"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="49"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -2060,15 +1999,15 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="12"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="49"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -2088,15 +2027,15 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="12"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="49"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -2116,15 +2055,15 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="12"/>
+      <c r="A45" s="47"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="49"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -2144,15 +2083,15 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="12"/>
+      <c r="A46" s="47"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="49"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -2172,15 +2111,15 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="12"/>
+      <c r="A47" s="47"/>
+      <c r="B47" s="48"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="49"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -2200,15 +2139,15 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="12"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="49"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -2228,15 +2167,15 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="12"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="49"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -2256,15 +2195,15 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="12"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="48"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="49"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -2284,15 +2223,15 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="10"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="12"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="50"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="52"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -2312,15 +2251,21 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="12"/>
+      <c r="A52" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" s="17"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="17"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="17"/>
+      <c r="I52" s="18"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -2340,15 +2285,15 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="12"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -2368,15 +2313,17 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="10"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="12"/>
+      <c r="A54" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="18"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -2396,15 +2343,19 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="10"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="12"/>
+      <c r="A55" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="18"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -2424,15 +2375,15 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="10"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="12"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="18"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -2452,15 +2403,15 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="10"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="12"/>
+      <c r="A57" s="3"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="18"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -2480,15 +2431,15 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="10"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="12"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="18"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -2508,15 +2459,15 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="10"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15"/>
+      <c r="A59" s="3"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="18"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -2536,21 +2487,17 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="28" t="s">
-        <v>23</v>
+      <c r="A60" s="25" t="s">
+        <v>20</v>
       </c>
-      <c r="B60" s="21"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="H60" s="21"/>
-      <c r="I60" s="22"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="11"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -2570,15 +2517,23 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
+      <c r="A61" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -2598,17 +2553,19 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="27" t="s">
-        <v>26</v>
+      <c r="A62" s="5">
+        <v>1</v>
       </c>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="22"/>
+      <c r="B62" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -2628,19 +2585,19 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>8</v>
+      <c r="A63" s="5">
+        <v>2</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="22"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -2660,15 +2617,19 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="22"/>
+      <c r="A64" s="5">
+        <v>3</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -2688,15 +2649,19 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="22"/>
+      <c r="A65" s="5">
+        <v>4</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -2716,15 +2681,19 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
-      <c r="I66" s="22"/>
+      <c r="A66" s="5">
+        <v>5</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -2744,15 +2713,19 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
-      <c r="I67" s="22"/>
+      <c r="A67" s="5">
+        <v>6</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -2772,17 +2745,19 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="25" t="s">
-        <v>28</v>
+      <c r="A68" s="5">
+        <v>7</v>
       </c>
-      <c r="B68" s="17"/>
+      <c r="B68" s="26" t="s">
+        <v>31</v>
+      </c>
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -2802,23 +2777,19 @@
       <c r="Z68" s="1"/>
     </row>
     <row r="69" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>29</v>
+      <c r="A69" s="5">
+        <v>8</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I69" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -2838,19 +2809,17 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
-        <v>1</v>
-      </c>
-      <c r="B70" s="23" t="s">
+      <c r="A70" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="10"/>
+      <c r="I70" s="11"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -2870,19 +2839,15 @@
       <c r="Z70" s="1"/>
     </row>
     <row r="71" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
-        <v>2</v>
-      </c>
-      <c r="B71" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
+      <c r="A71" s="27"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="11"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -2902,19 +2867,15 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
-        <v>3</v>
-      </c>
-      <c r="B72" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
+      <c r="A72" s="6"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="8"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -2934,19 +2895,15 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
-        <v>4</v>
-      </c>
-      <c r="B73" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
+      <c r="A73" s="6"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="8"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -2966,19 +2923,15 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
-        <v>5</v>
-      </c>
-      <c r="B74" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
+      <c r="A74" s="6"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="8"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -2998,19 +2951,15 @@
       <c r="Z74" s="1"/>
     </row>
     <row r="75" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
-        <v>6</v>
-      </c>
-      <c r="B75" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
+      <c r="A75" s="27"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="10"/>
+      <c r="G75" s="10"/>
+      <c r="H75" s="10"/>
+      <c r="I75" s="11"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -3030,19 +2979,17 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
-        <v>7</v>
+      <c r="A76" s="28" t="s">
+        <v>34</v>
       </c>
-      <c r="B76" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="11"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -3062,19 +3009,15 @@
       <c r="Z76" s="1"/>
     </row>
     <row r="77" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
-        <v>8</v>
-      </c>
-      <c r="B77" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
+      <c r="A77" s="27"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="10"/>
+      <c r="G77" s="10"/>
+      <c r="H77" s="10"/>
+      <c r="I77" s="11"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -3094,17 +3037,15 @@
       <c r="Z77" s="1"/>
     </row>
     <row r="78" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="17"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="17"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="17"/>
-      <c r="G78" s="17"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="18"/>
+      <c r="A78" s="27"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="10"/>
+      <c r="I78" s="11"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
@@ -3124,15 +3065,15 @@
       <c r="Z78" s="1"/>
     </row>
     <row r="79" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="16"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="18"/>
+      <c r="A79" s="27"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="10"/>
+      <c r="I79" s="11"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -3152,17 +3093,15 @@
       <c r="Z79" s="1"/>
     </row>
     <row r="80" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="18"/>
+      <c r="A80" s="27"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="10"/>
+      <c r="I80" s="11"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -3182,15 +3121,15 @@
       <c r="Z80" s="1"/>
     </row>
     <row r="81" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="16"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="18"/>
+      <c r="A81" s="27"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="10"/>
+      <c r="I81" s="11"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -3210,15 +3149,17 @@
       <c r="Z81" s="1"/>
     </row>
     <row r="82" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="16"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="17"/>
-      <c r="G82" s="17"/>
-      <c r="H82" s="17"/>
-      <c r="I82" s="18"/>
+      <c r="A82" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B82" s="10"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="10"/>
+      <c r="I82" s="11"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -3238,9 +3179,7 @@
       <c r="Z82" s="1"/>
     </row>
     <row r="83" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="19" t="s">
-        <v>43</v>
-      </c>
+      <c r="A83" s="29"/>
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
       <c r="D83" s="17"/>
@@ -3268,15 +3207,15 @@
       <c r="Z83" s="1"/>
     </row>
     <row r="84" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="20"/>
-      <c r="B84" s="21"/>
-      <c r="C84" s="21"/>
-      <c r="D84" s="21"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="22"/>
+      <c r="A84" s="29"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
+      <c r="G84" s="17"/>
+      <c r="H84" s="17"/>
+      <c r="I84" s="18"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -3296,15 +3235,15 @@
       <c r="Z84" s="1"/>
     </row>
     <row r="85" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="20"/>
-      <c r="B85" s="21"/>
-      <c r="C85" s="21"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="21"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="21"/>
-      <c r="I85" s="22"/>
+      <c r="A85" s="29"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="17"/>
+      <c r="G85" s="17"/>
+      <c r="H85" s="17"/>
+      <c r="I85" s="18"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -3324,15 +3263,15 @@
       <c r="Z85" s="1"/>
     </row>
     <row r="86" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
+      <c r="A86" s="29"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="17"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="17"/>
+      <c r="G86" s="17"/>
+      <c r="H86" s="17"/>
+      <c r="I86" s="18"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -3352,15 +3291,15 @@
       <c r="Z86" s="1"/>
     </row>
     <row r="87" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="17"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="17"/>
+      <c r="I87" s="18"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
@@ -7551,61 +7490,117 @@
       <c r="Y236" s="1"/>
       <c r="Z236" s="1"/>
     </row>
+    <row r="237" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+      <c r="F237" s="1"/>
+      <c r="G237" s="1"/>
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+      <c r="J237" s="1"/>
+      <c r="K237" s="1"/>
+      <c r="L237" s="1"/>
+      <c r="M237" s="1"/>
+      <c r="N237" s="1"/>
+      <c r="O237" s="1"/>
+      <c r="P237" s="1"/>
+      <c r="Q237" s="1"/>
+      <c r="R237" s="1"/>
+      <c r="S237" s="1"/>
+      <c r="T237" s="1"/>
+      <c r="U237" s="1"/>
+      <c r="V237" s="1"/>
+      <c r="W237" s="1"/>
+      <c r="X237" s="1"/>
+      <c r="Y237" s="1"/>
+      <c r="Z237" s="1"/>
+    </row>
+    <row r="238" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+      <c r="J238" s="1"/>
+      <c r="K238" s="1"/>
+      <c r="L238" s="1"/>
+      <c r="M238" s="1"/>
+      <c r="N238" s="1"/>
+      <c r="O238" s="1"/>
+      <c r="P238" s="1"/>
+      <c r="Q238" s="1"/>
+      <c r="R238" s="1"/>
+      <c r="S238" s="1"/>
+      <c r="T238" s="1"/>
+      <c r="U238" s="1"/>
+      <c r="V238" s="1"/>
+      <c r="W238" s="1"/>
+      <c r="X238" s="1"/>
+      <c r="Y238" s="1"/>
+      <c r="Z238" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A13:B17"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:I17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="G60:I60"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B64:I64"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="B67:I67"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
+  <mergeCells count="50">
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A81:I81"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="A87:I87"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="A86:I86"/>
     <mergeCell ref="A85:I85"/>
-    <mergeCell ref="B77:G77"/>
-    <mergeCell ref="A78:I78"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B68:G68"/>
+    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="A1:I2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>